--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q80_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03169788530341371</v>
+        <v>0.01577778918357779</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03169788530341371</v>
+        <v>0.01577778918357779</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04962103067609135</v>
+        <v>0.02523644511061465</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04962103067609135</v>
+        <v>0.02523644511061465</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09383378568028504</v>
+        <v>0.04772750643034643</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09383378568028504</v>
+        <v>0.04772750643034643</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1516142790164638</v>
+        <v>0.0769820498513531</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1516142790164638</v>
+        <v>0.0769820498513531</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2000393376929227</v>
+        <v>0.101782763368</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2000393376929227</v>
+        <v>0.101782763368</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2168850963843929</v>
+        <v>0.1102840351178698</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2168850963843929</v>
+        <v>0.1102840351178698</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.21207429579727</v>
+        <v>0.107800908260826</v>
       </c>
       <c r="C8" t="n">
-        <v>0.21207429579727</v>
+        <v>0.107800908260826</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1997303742820163</v>
+        <v>0.1015824330522249</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1997303742820163</v>
+        <v>0.1015824330522249</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1866551583222076</v>
+        <v>0.09486448007923987</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1866551583222076</v>
+        <v>0.09486448007923987</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1809107910963529</v>
+        <v>0.08940445068255531</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1809107910963529</v>
+        <v>0.08940445068255531</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
